--- a/Sample_BOM_PCBWay.xlsx
+++ b/Sample_BOM_PCBWay.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileSharing readOnlyRecommended="1"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cl\Dropbox\python-windows\getBOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\dropbox-sync\Dropbox\KICAD\PCBWAY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FF506C-F674-4253-B936-B9D96A068437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17348605-5292-451C-B0EF-B0B78A671A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="29820" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4635" yWindow="4635" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,30 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>Item #</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Designator</t>
-    </r>
   </si>
   <si>
     <r>
@@ -123,14 +103,274 @@
     <t>Your Instructions / Notes</t>
   </si>
   <si>
-    <t>BOM</t>
+    <t>C1, C2, C3, C4</t>
+  </si>
+  <si>
+    <t>100pF</t>
+  </si>
+  <si>
+    <t>C-US025-025X050</t>
+  </si>
+  <si>
+    <t>charhead-lib:CAP_1206_3216Metric_Pad1.33x1.80mm CL</t>
+  </si>
+  <si>
+    <t>CAPACITOR, American symbol</t>
+  </si>
+  <si>
+    <t>47pF to 300pF will work, or omit</t>
+  </si>
+  <si>
+    <t>C5, C6</t>
+  </si>
+  <si>
+    <t>470pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Component Count:</t>
+  </si>
+  <si>
+    <t>Ref</t>
+  </si>
+  <si>
+    <t>Qnty</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Cmp name</t>
+  </si>
+  <si>
+    <t>Footprint</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>C7, C8</t>
+  </si>
+  <si>
+    <t>.1uF</t>
+  </si>
+  <si>
+    <t>C-US025-024X044</t>
+  </si>
+  <si>
+    <t>C13, C14</t>
+  </si>
+  <si>
+    <t>.1Uf</t>
+  </si>
+  <si>
+    <t>C15, C17</t>
+  </si>
+  <si>
+    <t>FB1, FB2</t>
+  </si>
+  <si>
+    <t>whatever_u_got_injunkbox</t>
+  </si>
+  <si>
+    <t>FerriteBead_Small</t>
+  </si>
+  <si>
+    <t>charhead-lib:FerriteBeadSmall-Vert</t>
+  </si>
+  <si>
+    <t>Ferrite bead, small symbol</t>
+  </si>
+  <si>
+    <t>4 found on all SOIC version.  You must use beads or jumpers here.</t>
+  </si>
+  <si>
+    <t>IC2</t>
+  </si>
+  <si>
+    <t>TL084P</t>
+  </si>
+  <si>
+    <t>charhead-lib:IC SOIC-14 hand solder</t>
+  </si>
+  <si>
+    <t>OP AMP</t>
+  </si>
+  <si>
+    <t>Any good quality quad SOIC op amp will work</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>CVA</t>
+  </si>
+  <si>
+    <t>Conn_01x02_Pin</t>
+  </si>
+  <si>
+    <t>Connector_JST:JST_EH_B2B-EH-A_1x02_P2.50mm_Vertical</t>
+  </si>
+  <si>
+    <t>Generic connector, single row, 01x02, script generated</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>Audio Out</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>Audio In</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>POWER</t>
+  </si>
+  <si>
+    <t>Conn_01x04_Pin</t>
+  </si>
+  <si>
+    <t>Connector_JST:JST_EH_B4B-EH-A_1x04_P2.50mm_Vertical</t>
+  </si>
+  <si>
+    <t>Generic connector, single row, 01x04, script generated</t>
+  </si>
+  <si>
+    <t>J5</t>
+  </si>
+  <si>
+    <t>Header01</t>
+  </si>
+  <si>
+    <t>Conn_01x14_Pin</t>
+  </si>
+  <si>
+    <t>Connector_PinHeader_2.54mm:PinHeader_1x14_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>Generic connector, single row, 01x14, script generated</t>
+  </si>
+  <si>
+    <t>J9</t>
+  </si>
+  <si>
+    <t>Offset</t>
+  </si>
+  <si>
+    <t>J10</t>
+  </si>
+  <si>
+    <t>CVB</t>
+  </si>
+  <si>
+    <t>R1, R3, R4, R7</t>
+  </si>
+  <si>
+    <t>33K</t>
+  </si>
+  <si>
+    <t>R-US_0207/10</t>
+  </si>
+  <si>
+    <t>charhead-lib:R_1206_3216Metric_Pad1.30x1.75mm_SMD CL</t>
+  </si>
+  <si>
+    <t>RESISTOR, American symbol</t>
+  </si>
+  <si>
+    <t>R2, R11, R12, R14, R18, R19</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>adafruit_R-US_0207/10</t>
+  </si>
+  <si>
+    <t>R5, R6, R8, R9</t>
+  </si>
+  <si>
+    <t>R10, R15</t>
+  </si>
+  <si>
+    <t>0ohm</t>
+  </si>
+  <si>
+    <t>Omit to set bias offset of buffers using the "offset" JST connector</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>7.5K</t>
+  </si>
+  <si>
+    <t>R16, R17</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>SSM2164</t>
+  </si>
+  <si>
+    <t>DIL16</t>
+  </si>
+  <si>
+    <t>VCAxx64</t>
+  </si>
+  <si>
+    <t>Package_DIP:DIP-16_W7.62mm_Socket_LongPads</t>
+  </si>
+  <si>
+    <t>SOCKET Dual In Line</t>
+  </si>
+  <si>
+    <t>Use SOIC 2164 for all SOIC version</t>
+  </si>
+  <si>
+    <t>SV1</t>
+  </si>
+  <si>
+    <t>~</t>
+  </si>
+  <si>
+    <t>EURO_POWER_HEADERREGULAR</t>
+  </si>
+  <si>
+    <t>charhead-lib:Euro Power 10 Pin THT</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Designator</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,7 +381,21 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -177,14 +431,38 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF444444"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -203,8 +481,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -227,50 +511,183 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -623,13 +1040,35 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{85468641-3303-47BE-8BCE-E442531695A9}">
+  <we:reference id="29673e3c-d826-4f00-92ee-162334a52b1a" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;aa280bc4-3a29-44fa-87c9-4ed8344d404a&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I24"/>
+  <dimension ref="A2:K56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
     <col min="4" max="4" width="21.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="29.85546875" style="1" customWidth="1"/>
@@ -640,261 +1079,709 @@
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="19.5" customHeight="1">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="D2" s="12" t="s">
+    <row r="2" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="D2" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="42"/>
+      <c r="B3" s="42"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+    </row>
+    <row r="6" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15">
+      <c r="A7" s="6">
+        <v>1</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="1:11" ht="15">
+      <c r="A8" s="6">
+        <v>2</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="9"/>
+    </row>
+    <row r="9" spans="1:11" ht="15">
+      <c r="A9" s="6">
+        <v>3</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="15">
+      <c r="A10" s="6">
+        <v>4</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="34"/>
+    </row>
+    <row r="11" spans="1:11" ht="15">
+      <c r="A11" s="6">
+        <v>5</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" ht="15">
+      <c r="A12" s="6">
+        <v>6</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" ht="15">
+      <c r="A13" s="6">
+        <v>7</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" ht="15">
+      <c r="A14" s="6">
+        <v>8</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="1:11" ht="15">
+      <c r="A15" s="6">
         <v>9</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="6" spans="1:9" ht="28.5" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="5">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="5">
-        <v>2</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="5">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="5">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="5">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="5">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="5">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="5">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="5">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="5">
+      <c r="B15" s="19"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="1:11" ht="15">
+      <c r="A16" s="6">
         <v>10</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="5">
+      <c r="B16" s="19"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="9"/>
+    </row>
+    <row r="17" spans="1:9" ht="15">
+      <c r="A17" s="6">
         <v>11</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="5">
+      <c r="A18" s="6">
         <v>12</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="5">
+      <c r="B18" s="12"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="1:9" ht="15">
+      <c r="A19" s="6">
         <v>13</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="14"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>14</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="5">
+      <c r="A21" s="16">
         <v>15</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+    </row>
+    <row r="22" spans="1:9" ht="18" customHeight="1">
+      <c r="A22" s="6">
+        <v>16</v>
+      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="29"/>
+    </row>
+    <row r="23" spans="1:9" ht="15">
+      <c r="A23" s="6">
+        <v>17</v>
+      </c>
+      <c r="B23" s="22"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="29"/>
+    </row>
+    <row r="24" spans="1:9" ht="15">
+      <c r="A24" s="6">
+        <v>18</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="38"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
+      <c r="I24" s="29"/>
+    </row>
+    <row r="25" spans="1:9" ht="15">
+      <c r="A25" s="6">
+        <v>19</v>
+      </c>
+      <c r="B25" s="22"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="29"/>
+    </row>
+    <row r="26" spans="1:9" s="2" customFormat="1" ht="15">
+      <c r="A26" s="6">
+        <v>20</v>
+      </c>
+      <c r="B26" s="22"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="29"/>
+    </row>
+    <row r="27" spans="1:9" ht="15">
+      <c r="A27" s="6">
+        <v>21</v>
+      </c>
+      <c r="B27" s="22"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="29"/>
+    </row>
+    <row r="28" spans="1:9" ht="15">
+      <c r="A28" s="6">
+        <v>22</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="29"/>
+    </row>
+    <row r="29" spans="1:9" ht="15">
+      <c r="A29" s="6">
+        <v>23</v>
+      </c>
+      <c r="B29" s="22"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="29"/>
+    </row>
+    <row r="30" spans="1:9" ht="15">
+      <c r="A30" s="6">
+        <v>24</v>
+      </c>
+      <c r="B30" s="22"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="29"/>
+    </row>
+    <row r="31" spans="1:9" ht="15">
+      <c r="A31" s="6">
+        <v>25</v>
+      </c>
+      <c r="B31" s="22"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="29"/>
+    </row>
+    <row r="32" spans="1:9" ht="15">
+      <c r="A32" s="6">
+        <v>26</v>
+      </c>
+      <c r="B32" s="22"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="29"/>
+    </row>
+    <row r="33" spans="1:9" ht="15">
+      <c r="A33" s="6">
+        <v>27</v>
+      </c>
+      <c r="B33" s="22"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="29"/>
+    </row>
+    <row r="34" spans="1:9" ht="15">
+      <c r="A34" s="6">
+        <v>28</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="31"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="29"/>
+    </row>
+    <row r="35" spans="1:9" ht="15">
+      <c r="A35" s="6">
+        <v>29</v>
+      </c>
+      <c r="B35" s="22"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="29"/>
+    </row>
+    <row r="36" spans="1:9" ht="15">
+      <c r="A36" s="6">
+        <v>30</v>
+      </c>
+      <c r="B36" s="22"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="29"/>
+    </row>
+    <row r="37" spans="1:9" ht="15">
+      <c r="A37" s="6">
+        <v>31</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="29"/>
+    </row>
+    <row r="38" spans="1:9" ht="15">
+      <c r="A38" s="6">
+        <v>32</v>
+      </c>
+      <c r="B38" s="22"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="29"/>
+    </row>
+    <row r="39" spans="1:9" ht="15">
+      <c r="A39" s="6">
+        <v>33</v>
+      </c>
+      <c r="B39" s="22"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="29"/>
+    </row>
+    <row r="40" spans="1:9" ht="15">
+      <c r="A40" s="6">
+        <v>34</v>
+      </c>
+      <c r="B40" s="22"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="29"/>
+    </row>
+    <row r="41" spans="1:9" ht="15">
+      <c r="A41" s="6">
+        <v>35</v>
+      </c>
+      <c r="B41" s="22"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="29"/>
+    </row>
+    <row r="42" spans="1:9" ht="15">
+      <c r="A42" s="6">
+        <v>36</v>
+      </c>
+      <c r="B42" s="22"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="29"/>
+    </row>
+    <row r="43" spans="1:9" ht="15">
+      <c r="A43" s="6">
+        <v>37</v>
+      </c>
+      <c r="B43" s="22"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="29"/>
+    </row>
+    <row r="44" spans="1:9" ht="15">
+      <c r="A44" s="6">
+        <v>38</v>
+      </c>
+      <c r="B44" s="22"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="29"/>
+    </row>
+    <row r="45" spans="1:9" ht="15">
+      <c r="A45" s="6">
+        <v>39</v>
+      </c>
+      <c r="B45" s="22"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="29"/>
+    </row>
+    <row r="46" spans="1:9" ht="15">
+      <c r="A46" s="6">
+        <v>40</v>
+      </c>
+      <c r="B46" s="22"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="29"/>
+    </row>
+    <row r="47" spans="1:9" ht="15">
+      <c r="A47" s="6">
+        <v>41</v>
+      </c>
+      <c r="B47" s="22"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="29"/>
+    </row>
+    <row r="48" spans="1:9" ht="15">
+      <c r="A48" s="6">
+        <v>42</v>
+      </c>
+      <c r="B48" s="22"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="38"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="29"/>
+    </row>
+    <row r="49" spans="1:9" ht="15">
+      <c r="A49" s="6">
+        <v>43</v>
+      </c>
+      <c r="B49" s="22"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="29"/>
+    </row>
+    <row r="50" spans="1:9" ht="15">
+      <c r="A50" s="6">
+        <v>44</v>
+      </c>
+      <c r="B50" s="22"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="29"/>
+    </row>
+    <row r="51" spans="1:9" ht="15">
+      <c r="A51" s="6">
+        <v>45</v>
+      </c>
+      <c r="B51" s="22"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="29"/>
+    </row>
+    <row r="52" spans="1:9" ht="15">
+      <c r="A52" s="6">
+        <v>46</v>
+      </c>
+      <c r="B52" s="22"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="29"/>
+    </row>
+    <row r="53" spans="1:9" ht="15">
+      <c r="A53" s="6">
+        <v>47</v>
+      </c>
+      <c r="B53" s="22"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="29"/>
+    </row>
+    <row r="54" spans="1:9" ht="15">
+      <c r="A54" s="6">
+        <v>48</v>
+      </c>
+      <c r="B54" s="22"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="29"/>
+    </row>
+    <row r="55" spans="1:9" ht="15">
+      <c r="A55" s="6">
+        <v>49</v>
+      </c>
+      <c r="B55" s="22"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="29"/>
+    </row>
+    <row r="56" spans="1:9" ht="15">
+      <c r="A56" s="6">
+        <v>50</v>
+      </c>
+      <c r="B56" s="22"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -909,9 +1796,674 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="10">
+        <v>47</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="10">
+        <v>4</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="10">
+        <v>2</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10">
+        <v>2</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="10">
+        <v>2</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="10">
+        <v>2</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="10">
+        <v>2</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="10">
+        <v>1</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="10">
+        <v>1</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="10">
+        <v>1</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="10">
+        <v>1</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="10">
+        <v>1</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="10">
+        <v>1</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="10">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="10">
+        <v>4</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="10">
+        <v>6</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="10">
+        <v>4</v>
+      </c>
+      <c r="C19" s="10">
+        <v>500</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="10">
+        <v>2</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="10">
+        <v>1</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="10">
+        <v>2</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="10">
+        <v>1</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="10">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
 </worksheet>
